--- a/data/trans_dic/P05B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P05B_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,38</t>
+          <t>1,19; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,77</t>
+          <t>0,57; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,44</t>
+          <t>1,88; 4,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,33</t>
+          <t>0,13; 1,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,47</t>
+          <t>1,78; 3,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,81</t>
+          <t>0,12; 0,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,57</t>
+          <t>0,48; 1,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,56</t>
+          <t>0,11; 0,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,44</t>
+          <t>1,57; 3,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,71</t>
+          <t>0,92; 2,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,06</t>
+          <t>0,6; 2,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,02</t>
+          <t>0,14; 1,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,9</t>
+          <t>3,28; 5,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,84</t>
+          <t>1,71; 3,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,67</t>
+          <t>0,98; 2,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,3; 1,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,32</t>
+          <t>2,61; 4,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,8</t>
+          <t>1,54; 2,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,11</t>
+          <t>0,94; 2,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,9</t>
+          <t>0,33; 0,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,14</t>
+          <t>1,33; 4,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,56</t>
+          <t>1,21; 3,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,93</t>
+          <t>0,83; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,56</t>
+          <t>0,17; 1,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,67</t>
+          <t>2,64; 5,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,11</t>
+          <t>0,52; 2,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,97</t>
+          <t>2,2; 5,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,76</t>
+          <t>0,16; 0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,29</t>
+          <t>2,31; 4,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,31</t>
+          <t>1,02; 2,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,34</t>
+          <t>1,78; 3,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,92</t>
+          <t>0,26; 1,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1137,57 +1137,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,17</t>
+          <t>3,32; 6,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,63</t>
+          <t>1,48; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,25</t>
+          <t>0,76; 2,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,32</t>
+          <t>1,8; 3,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,26</t>
+          <t>5,26; 8,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,11</t>
+          <t>1,13; 2,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,04</t>
+          <t>1,8; 3,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,21</t>
+          <t>2,3; 4,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,71</t>
+          <t>4,6; 6,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,89</t>
+          <t>1,52; 2,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,93</t>
+          <t>1,46; 2,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,61</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,86</t>
+          <t>0,98; 1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,61</t>
+          <t>0,8; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,43</t>
+          <t>4,0; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,09</t>
+          <t>1,22; 2,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,75</t>
+          <t>1,67; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,59</t>
+          <t>0,99; 1,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,35</t>
+          <t>3,38; 4,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,97</t>
+          <t>1,35; 2,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,1</t>
+          <t>1,45; 2,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,42</t>
+          <t>0,95; 1,43</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3499</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8278; 23444</t>
+          <t>8274; 24400</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6494</t>
+          <t>0; 6140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4188; 18636</t>
+          <t>3864; 17224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 5183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13334; 30569</t>
+          <t>12951; 30594</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>934; 7743</t>
+          <t>930; 7651</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>903; 8902</t>
+          <t>900; 9638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>644; 4419</t>
+          <t>697; 4481</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24913; 47904</t>
+          <t>24570; 48210</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1740; 11263</t>
+          <t>1682; 10098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6058; 21115</t>
+          <t>6429; 20944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1454; 7671</t>
+          <t>1496; 7775</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11289</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14202; 33044</t>
+          <t>15086; 34817</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9163; 27444</t>
+          <t>9358; 26767</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6534; 21071</t>
+          <t>6153; 21529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1186; 12166</t>
+          <t>1414; 11318</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31523; 57040</t>
+          <t>31676; 56997</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17791; 39492</t>
+          <t>17556; 38148</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10509; 27736</t>
+          <t>10140; 26812</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3208; 13176</t>
+          <t>3241; 12170</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50341; 83280</t>
+          <t>50308; 83216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30226; 57212</t>
+          <t>31358; 58747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19521; 43444</t>
+          <t>19413; 43988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5763; 19342</t>
+          <t>6966; 19227</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>8264</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9093; 28086</t>
+          <t>9052; 27522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8967; 26950</t>
+          <t>9204; 28567</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6238; 22195</t>
+          <t>6267; 20680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1104; 10949</t>
+          <t>1341; 11929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18049; 38789</t>
+          <t>18041; 38439</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4030; 16353</t>
+          <t>4013; 16311</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16840; 38902</t>
+          <t>17244; 39146</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>629; 7074</t>
+          <t>1331; 7569</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30645; 58383</t>
+          <t>31499; 58010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15160; 35424</t>
+          <t>15676; 36809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26779; 51429</t>
+          <t>27452; 52488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2715; 15067</t>
+          <t>4147; 16518</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>62420</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32330; 57966</t>
+          <t>31183; 57823</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14388; 34015</t>
+          <t>13855; 34558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6621; 20979</t>
+          <t>7065; 22544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17410; 40051</t>
+          <t>17828; 39410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53979; 85739</t>
+          <t>54593; 87031</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13378; 32491</t>
+          <t>11756; 29796</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18727; 41899</t>
+          <t>18612; 39482</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24015; 45866</t>
+          <t>25532; 45280</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93399; 132642</t>
+          <t>91060; 132838</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30881; 57315</t>
+          <t>30052; 57136</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31006; 57752</t>
+          <t>28771; 56132</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47160; 77920</t>
+          <t>49051; 81223</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77821; 118038</t>
+          <t>79226; 119159</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42992; 73995</t>
+          <t>42094; 72273</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33487; 62825</t>
+          <t>33076; 61293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25729; 55549</t>
+          <t>28070; 53861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>135783; 183332</t>
+          <t>135032; 183299</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42825; 73961</t>
+          <t>43147; 74619</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59492; 97187</t>
+          <t>58836; 94563</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33726; 59068</t>
+          <t>36797; 60395</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>224001; 289091</t>
+          <t>225037; 289010</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93701; 137168</t>
+          <t>94193; 141390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100222; 145077</t>
+          <t>100422; 147346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65425; 101869</t>
+          <t>68745; 103457</t>
         </is>
       </c>
     </row>
